--- a/templates/project-management/simple-task-list.xlsx
+++ b/templates/project-management/simple-task-list.xlsx
@@ -1,9 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\dev\sheetxl\templates-workbook\templates\project-management\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC8B9D2B-0258-4752-92D2-2AA1A1E68AE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView/>
+    <workbookView xWindow="1380" yWindow="1665" windowWidth="27420" windowHeight="12255" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tasks" sheetId="1" r:id="rId1"/>
@@ -11,6 +18,20 @@
   <definedNames>
     <definedName name="AsOf">Tasks!$I$4</definedName>
   </definedNames>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -124,8 +145,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="3">
-    <numFmt numFmtId="164" formatCode="mmm d, yyyy"/>
-    <numFmt numFmtId="165" formatCode="mmm d"/>
+    <numFmt numFmtId="164" formatCode="mmm\ d\,\ yyyy"/>
+    <numFmt numFmtId="165" formatCode="mmm\ d"/>
     <numFmt numFmtId="166" formatCode="0;&quot;-&quot;0;0"/>
   </numFmts>
   <fonts count="7" x14ac:knownFonts="1">
@@ -194,7 +215,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -232,11 +253,24 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFCBD2D9"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFCBD2D9"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFCBD2D9"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -250,7 +284,7 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="9" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="5" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -267,11 +301,212 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" customBuiltin="1"/>
   </cellStyles>
-  <dxfs count="4">
+  <dxfs count="15">
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <name val="Calibri"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FF1F4E79"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color rgb="FFCBD2D9"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFCBD2D9"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFCBD2D9"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFCBD2D9"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="0;&quot;-&quot;0;0"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color rgb="FFCBD2D9"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFCBD2D9"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFCBD2D9"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFCBD2D9"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="mmm\ d"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color rgb="FFCBD2D9"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFCBD2D9"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFCBD2D9"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFCBD2D9"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="mmm\ d"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color rgb="FFCBD2D9"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFCBD2D9"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFCBD2D9"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFCBD2D9"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color rgb="FFCBD2D9"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFCBD2D9"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFCBD2D9"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFCBD2D9"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color rgb="FFCBD2D9"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFCBD2D9"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFCBD2D9"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFCBD2D9"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color rgb="FFCBD2D9"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFCBD2D9"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFCBD2D9"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFCBD2D9"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color rgb="FFCBD2D9"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFCBD2D9"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFCBD2D9"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFCBD2D9"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color rgb="FFCBD2D9"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFB42318"/>
+      </font>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF1F4E79"/>
@@ -279,7 +514,8 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FFB42318"/>
+        <strike/>
+        <color rgb="FF616E7C"/>
       </font>
     </dxf>
     <dxf>
@@ -291,12 +527,6 @@
           <fgColor rgb="FFFDE4E1"/>
         </patternFill>
       </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike/>
-        <color rgb="FF616E7C"/>
-      </font>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -309,6 +539,25 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{A61A000D-5665-4D7F-BD50-E9DC21498128}" name="Table1" displayName="Table1" ref="B7:I37" totalsRowShown="0" headerRowDxfId="0" dataDxfId="1" tableBorderDxfId="10">
+  <autoFilter ref="B7:I37" xr:uid="{A61A000D-5665-4D7F-BD50-E9DC21498128}"/>
+  <tableColumns count="8">
+    <tableColumn id="1" xr3:uid="{FCFDA734-FCB4-477B-8935-B7EF3120F6CC}" name="Task" dataDxfId="9"/>
+    <tableColumn id="2" xr3:uid="{4C50AC2C-A641-4EA6-8CF4-3944E332FAFF}" name="Owner" dataDxfId="8"/>
+    <tableColumn id="3" xr3:uid="{43C5296D-5401-4228-8C7C-BC5A72FCA05F}" name="Priority" dataDxfId="7"/>
+    <tableColumn id="4" xr3:uid="{15247CBE-DF95-4EFE-944C-3D6ED71143BC}" name="Status" dataDxfId="6"/>
+    <tableColumn id="5" xr3:uid="{7DDECFB8-51DD-4000-8627-E1774B25B126}" name="Start" dataDxfId="5"/>
+    <tableColumn id="6" xr3:uid="{B8EC6C1B-1E35-4C9C-B25A-AFDB5F416C6E}" name="Due" dataDxfId="4"/>
+    <tableColumn id="7" xr3:uid="{BDE005C6-C823-4DA6-851D-FA4CD3F3AB47}" name="Days left" dataDxfId="3">
+      <calculatedColumnFormula>IF(OR($G8="",$E8="Done"),"",$G8-AsOf)</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="8" xr3:uid="{CD7F4706-A3AD-4DCC-B9B9-C135CE509C96}" name="Notes" dataDxfId="2"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium16" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -489,7 +738,6 @@
             </a:gs>
           </a:gsLst>
           <a:path path="circle"/>
-          <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
@@ -507,7 +755,6 @@
             </a:gs>
           </a:gsLst>
           <a:path path="circle"/>
-          <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
@@ -518,31 +765,31 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="B2:I37"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="2.3984375" customWidth="1"/>
+    <col min="1" max="1" width="2.42578125" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
     <col min="3" max="3" width="10" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
-    <col min="5" max="5" width="12.5" customWidth="1"/>
+    <col min="4" max="4" width="9.7109375" customWidth="1"/>
+    <col min="5" max="5" width="12.42578125" customWidth="1"/>
     <col min="6" max="7" width="8" customWidth="1"/>
-    <col min="8" max="8" width="10" customWidth="1"/>
+    <col min="8" max="8" width="10.85546875" customWidth="1"/>
     <col min="9" max="9" width="26" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:9" ht="23.25" x14ac:dyDescent="0.35">
       <c r="B2" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B3" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="4" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B4" s="3" t="s">
         <v>2</v>
       </c>
@@ -563,10 +810,10 @@
       </c>
       <c r="I4" s="5">
         <f ca="1">TODAY()</f>
-        <v>46288</v>
-      </c>
-    </row>
-    <row r="5" x14ac:dyDescent="0.25">
+        <v>46318</v>
+      </c>
+    </row>
+    <row r="5" spans="2:9" ht="21" x14ac:dyDescent="0.35">
       <c r="B5" s="6">
         <f t="shared" ref="B5:E5" si="0">COUNTIF($E$8:$E$37,B4)</f>
         <v>4</v>
@@ -588,7 +835,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="7" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B7" s="8" t="s">
         <v>8</v>
       </c>
@@ -614,7 +861,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="8" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B8" s="9" t="s">
         <v>16</v>
       </c>
@@ -641,7 +888,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="9" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B9" s="9" t="s">
         <v>20</v>
       </c>
@@ -666,7 +913,7 @@
       </c>
       <c r="I9" s="13"/>
     </row>
-    <row r="10" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B10" s="9" t="s">
         <v>22</v>
       </c>
@@ -686,14 +933,14 @@
         <v>46290</v>
       </c>
       <c r="H10" s="12">
-        <f t="shared" si="1"/>
-        <v>2</v>
+        <f t="shared" ca="1" si="1"/>
+        <v>-28</v>
       </c>
       <c r="I10" s="13" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="11" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B11" s="9" t="s">
         <v>25</v>
       </c>
@@ -713,14 +960,14 @@
         <v>46297</v>
       </c>
       <c r="H11" s="12">
-        <f t="shared" si="1"/>
-        <v>9</v>
+        <f t="shared" ca="1" si="1"/>
+        <v>-21</v>
       </c>
       <c r="I11" s="13" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="12" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B12" s="9" t="s">
         <v>28</v>
       </c>
@@ -740,12 +987,12 @@
         <v>46304</v>
       </c>
       <c r="H12" s="12">
-        <f t="shared" si="1"/>
-        <v>16</v>
+        <f t="shared" ca="1" si="1"/>
+        <v>-14</v>
       </c>
       <c r="I12" s="13"/>
     </row>
-    <row r="13" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B13" s="9" t="s">
         <v>30</v>
       </c>
@@ -765,12 +1012,12 @@
         <v>46325</v>
       </c>
       <c r="H13" s="12">
-        <f t="shared" si="1"/>
-        <v>37</v>
+        <f t="shared" ca="1" si="1"/>
+        <v>7</v>
       </c>
       <c r="I13" s="13"/>
     </row>
-    <row r="14" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B14" s="9" t="s">
         <v>31</v>
       </c>
@@ -790,12 +1037,12 @@
         <v>46339</v>
       </c>
       <c r="H14" s="12">
-        <f t="shared" si="1"/>
-        <v>51</v>
+        <f t="shared" ca="1" si="1"/>
+        <v>21</v>
       </c>
       <c r="I14" s="13"/>
     </row>
-    <row r="15" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B15" s="9" t="s">
         <v>32</v>
       </c>
@@ -815,12 +1062,12 @@
         <v>46346</v>
       </c>
       <c r="H15" s="12">
-        <f t="shared" si="1"/>
-        <v>58</v>
+        <f t="shared" ca="1" si="1"/>
+        <v>28</v>
       </c>
       <c r="I15" s="13"/>
     </row>
-    <row r="16" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B16" s="9"/>
       <c r="C16" s="9"/>
       <c r="D16" s="10"/>
@@ -833,7 +1080,7 @@
       </c>
       <c r="I16" s="13"/>
     </row>
-    <row r="17" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B17" s="9"/>
       <c r="C17" s="9"/>
       <c r="D17" s="10"/>
@@ -846,7 +1093,7 @@
       </c>
       <c r="I17" s="13"/>
     </row>
-    <row r="18" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B18" s="9"/>
       <c r="C18" s="9"/>
       <c r="D18" s="10"/>
@@ -859,7 +1106,7 @@
       </c>
       <c r="I18" s="13"/>
     </row>
-    <row r="19" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B19" s="9"/>
       <c r="C19" s="9"/>
       <c r="D19" s="10"/>
@@ -872,7 +1119,7 @@
       </c>
       <c r="I19" s="13"/>
     </row>
-    <row r="20" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B20" s="9"/>
       <c r="C20" s="9"/>
       <c r="D20" s="10"/>
@@ -885,7 +1132,7 @@
       </c>
       <c r="I20" s="13"/>
     </row>
-    <row r="21" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B21" s="9"/>
       <c r="C21" s="9"/>
       <c r="D21" s="10"/>
@@ -898,7 +1145,7 @@
       </c>
       <c r="I21" s="13"/>
     </row>
-    <row r="22" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B22" s="9"/>
       <c r="C22" s="9"/>
       <c r="D22" s="10"/>
@@ -911,7 +1158,7 @@
       </c>
       <c r="I22" s="13"/>
     </row>
-    <row r="23" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B23" s="9"/>
       <c r="C23" s="9"/>
       <c r="D23" s="10"/>
@@ -924,7 +1171,7 @@
       </c>
       <c r="I23" s="13"/>
     </row>
-    <row r="24" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B24" s="9"/>
       <c r="C24" s="9"/>
       <c r="D24" s="10"/>
@@ -937,7 +1184,7 @@
       </c>
       <c r="I24" s="13"/>
     </row>
-    <row r="25" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B25" s="9"/>
       <c r="C25" s="9"/>
       <c r="D25" s="10"/>
@@ -950,7 +1197,7 @@
       </c>
       <c r="I25" s="13"/>
     </row>
-    <row r="26" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B26" s="9"/>
       <c r="C26" s="9"/>
       <c r="D26" s="10"/>
@@ -963,7 +1210,7 @@
       </c>
       <c r="I26" s="13"/>
     </row>
-    <row r="27" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B27" s="9"/>
       <c r="C27" s="9"/>
       <c r="D27" s="10"/>
@@ -976,7 +1223,7 @@
       </c>
       <c r="I27" s="13"/>
     </row>
-    <row r="28" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B28" s="9"/>
       <c r="C28" s="9"/>
       <c r="D28" s="10"/>
@@ -989,7 +1236,7 @@
       </c>
       <c r="I28" s="13"/>
     </row>
-    <row r="29" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B29" s="9"/>
       <c r="C29" s="9"/>
       <c r="D29" s="10"/>
@@ -1002,7 +1249,7 @@
       </c>
       <c r="I29" s="13"/>
     </row>
-    <row r="30" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B30" s="9"/>
       <c r="C30" s="9"/>
       <c r="D30" s="10"/>
@@ -1015,7 +1262,7 @@
       </c>
       <c r="I30" s="13"/>
     </row>
-    <row r="31" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B31" s="9"/>
       <c r="C31" s="9"/>
       <c r="D31" s="10"/>
@@ -1028,7 +1275,7 @@
       </c>
       <c r="I31" s="13"/>
     </row>
-    <row r="32" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B32" s="9"/>
       <c r="C32" s="9"/>
       <c r="D32" s="10"/>
@@ -1041,7 +1288,7 @@
       </c>
       <c r="I32" s="13"/>
     </row>
-    <row r="33" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B33" s="9"/>
       <c r="C33" s="9"/>
       <c r="D33" s="10"/>
@@ -1054,7 +1301,7 @@
       </c>
       <c r="I33" s="13"/>
     </row>
-    <row r="34" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B34" s="9"/>
       <c r="C34" s="9"/>
       <c r="D34" s="10"/>
@@ -1067,7 +1314,7 @@
       </c>
       <c r="I34" s="13"/>
     </row>
-    <row r="35" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B35" s="9"/>
       <c r="C35" s="9"/>
       <c r="D35" s="10"/>
@@ -1080,7 +1327,7 @@
       </c>
       <c r="I35" s="13"/>
     </row>
-    <row r="36" x14ac:dyDescent="0.25">
+    <row r="36" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B36" s="9"/>
       <c r="C36" s="9"/>
       <c r="D36" s="10"/>
@@ -1093,46 +1340,49 @@
       </c>
       <c r="I36" s="13"/>
     </row>
-    <row r="37" x14ac:dyDescent="0.25">
-      <c r="B37" s="9"/>
-      <c r="C37" s="9"/>
-      <c r="D37" s="10"/>
-      <c r="E37" s="10"/>
-      <c r="F37" s="11"/>
-      <c r="G37" s="11"/>
-      <c r="H37" s="12" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="I37" s="13"/>
+    <row r="37" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B37" s="14"/>
+      <c r="C37" s="14"/>
+      <c r="D37" s="15"/>
+      <c r="E37" s="15"/>
+      <c r="F37" s="16"/>
+      <c r="G37" s="16"/>
+      <c r="H37" s="17" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="I37" s="14"/>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="B8:I37">
+    <cfRule type="expression" dxfId="14" priority="3">
+      <formula>AND($E8&lt;&gt;"Done",ISNUMBER($H8),$H8&lt;0)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="13" priority="4">
+      <formula>$E8="Done"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="D8:D37">
-    <cfRule type="expression" dxfId="0" priority="1">
+    <cfRule type="expression" dxfId="12" priority="1">
       <formula>$D8="High"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E8:E37">
-    <cfRule type="expression" dxfId="1" priority="2">
+    <cfRule type="expression" dxfId="11" priority="2">
       <formula>$E8="Blocked"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B8:I37">
-    <cfRule type="expression" dxfId="2" priority="3">
-      <formula>AND($E8&lt;&gt;"Done",ISNUMBER($H8),$H8&lt;0)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="3" priority="4">
-      <formula>$E8="Done"</formula>
-    </cfRule>
-  </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" errorStyle="stop" sqref="E8:E37">
+    <dataValidation type="list" allowBlank="1" sqref="E8:E37" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"Not started,In progress,Blocked,Done"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" errorStyle="stop" sqref="D8:D37">
+    <dataValidation type="list" allowBlank="1" sqref="D8:D37" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>"High,Medium,Low"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>